--- a/results/q3_output/表A_调度前后峰谷差对比.xlsx
+++ b/results/q3_output/表A_调度前后峰谷差对比.xlsx
@@ -510,13 +510,13 @@
         <v>2202</v>
       </c>
       <c r="E3" t="n">
-        <v>1521.8</v>
+        <v>1299.7</v>
       </c>
       <c r="F3" t="n">
-        <v>30.89009990917348</v>
+        <v>40.97638510445051</v>
       </c>
       <c r="G3" t="n">
-        <v>9.007766771724455</v>
+        <v>15.44188589438478</v>
       </c>
     </row>
     <row r="4">
@@ -564,13 +564,13 @@
         <v>2063</v>
       </c>
       <c r="E5" t="n">
-        <v>1465.4</v>
+        <v>1257.6</v>
       </c>
       <c r="F5" t="n">
-        <v>28.96752302472127</v>
+        <v>39.04023267086767</v>
       </c>
       <c r="G5" t="n">
-        <v>8.906300128328517</v>
+        <v>15.26794307713461</v>
       </c>
     </row>
     <row r="6">
@@ -618,13 +618,13 @@
         <v>1521</v>
       </c>
       <c r="E7" t="n">
-        <v>1094.2</v>
+        <v>940.8</v>
       </c>
       <c r="F7" t="n">
-        <v>28.06048652202498</v>
+        <v>38.14595660749507</v>
       </c>
       <c r="G7" t="n">
-        <v>9.157703172533672</v>
+        <v>15.69891972434345</v>
       </c>
     </row>
     <row r="8">
@@ -633,7 +633,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -645,10 +645,10 @@
         <v>1395</v>
       </c>
       <c r="E8" t="n">
-        <v>1090</v>
+        <v>1092.9</v>
       </c>
       <c r="F8" t="n">
-        <v>21.86379928315412</v>
+        <v>21.65591397849462</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -660,7 +660,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -672,13 +672,13 @@
         <v>1969</v>
       </c>
       <c r="E9" t="n">
-        <v>1280</v>
+        <v>1081.5</v>
       </c>
       <c r="F9" t="n">
-        <v>34.99238191975622</v>
+        <v>45.07364144235653</v>
       </c>
       <c r="G9" t="n">
-        <v>10.43660789252728</v>
+        <v>17.89132781576106</v>
       </c>
     </row>
     <row r="10">
@@ -687,7 +687,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -726,13 +726,13 @@
         <v>1506</v>
       </c>
       <c r="E11" t="n">
-        <v>1021.2</v>
+        <v>869.8</v>
       </c>
       <c r="F11" t="n">
-        <v>32.19123505976096</v>
+        <v>42.24435590969456</v>
       </c>
       <c r="G11" t="n">
-        <v>9.264228313518267</v>
+        <v>15.88153425174561</v>
       </c>
     </row>
     <row r="12">
@@ -780,13 +780,13 @@
         <v>1750</v>
       </c>
       <c r="E13" t="n">
-        <v>1168.6</v>
+        <v>992.3999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>33.22285714285715</v>
+        <v>43.29142857142858</v>
       </c>
       <c r="G13" t="n">
-        <v>10.86360196746122</v>
+        <v>18.62331765850495</v>
       </c>
     </row>
     <row r="14">
@@ -795,7 +795,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -834,13 +834,13 @@
         <v>719</v>
       </c>
       <c r="E15" t="n">
-        <v>504.6</v>
+        <v>431.9</v>
       </c>
       <c r="F15" t="n">
-        <v>29.81919332406119</v>
+        <v>39.93045897079277</v>
       </c>
       <c r="G15" t="n">
-        <v>10.08425034387895</v>
+        <v>17.2872863037925</v>
       </c>
     </row>
     <row r="16">
@@ -849,7 +849,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -942,13 +942,13 @@
         <v>1210</v>
       </c>
       <c r="E19" t="n">
-        <v>838.4</v>
+        <v>772</v>
       </c>
       <c r="F19" t="n">
-        <v>30.7107438016529</v>
+        <v>36.19834710743802</v>
       </c>
       <c r="G19" t="n">
-        <v>9.956554460864808</v>
+        <v>13.59705675272286</v>
       </c>
     </row>
     <row r="20">
@@ -957,7 +957,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -996,13 +996,13 @@
         <v>899</v>
       </c>
       <c r="E21" t="n">
-        <v>603.4</v>
+        <v>512.5999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>32.88097886540601</v>
+        <v>42.98109010011125</v>
       </c>
       <c r="G21" t="n">
-        <v>10.93176395007342</v>
+        <v>18.74016677155444</v>
       </c>
     </row>
     <row r="22">
@@ -1023,13 +1023,13 @@
         <v>14057</v>
       </c>
       <c r="E22" t="n">
-        <v>9668.6</v>
+        <v>8243.9</v>
       </c>
       <c r="F22" t="n">
-        <v>31.21860994522302</v>
+        <v>41.35377392046667</v>
       </c>
       <c r="G22" t="n">
-        <v>10.23029702159518</v>
+        <v>17.53765203702033</v>
       </c>
     </row>
     <row r="23">
